--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46244.739308379634</v>
+        <v>46245.748681655095</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>42</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -211,19 +211,19 @@
     <t xml:space="preserve">Propuesta Motor  ot 4387 </t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1217303695864968</t>
+  </si>
+  <si>
+    <t>Ingenieria basica nucleo rodete   ot 4387</t>
+  </si>
+  <si>
+    <t>Propuesta Alabes ot 4387,Propuesta rodete ot 4387</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1217303695864968</t>
-  </si>
-  <si>
-    <t>Ingenieria basica nucleo rodete   ot 4387</t>
-  </si>
-  <si>
-    <t>Propuesta Alabes ot 4387,Propuesta rodete ot 4387</t>
   </si>
   <si>
     <t>1217118826927689</t>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46246.171491284724</v>
+        <v>46247.20498152778</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -1850,29 +1850,29 @@
       <c r="R9" s="9">
         <v>46245</v>
       </c>
-      <c r="S9" s="7" t="s">
-        <v>46</v>
+      <c r="S9" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T9" s="10">
         <v>0</v>
       </c>
       <c r="U9" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46244.588363981486</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46244.626240219906</v>
+        <v>46247.17175421296</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>26</v>
@@ -1905,7 +1905,7 @@
         <v>38</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q10" s="5">
         <v>46247</v>
@@ -1914,13 +1914,13 @@
         <v>46245</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T10" s="6">
         <v>0</v>
       </c>
       <c r="U10" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -1977,13 +1977,13 @@
         <v>46245</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T11" s="10">
         <v>0</v>
       </c>
       <c r="U11" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46246.17149354167</v>
+        <v>46247.20497636574</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>57</v>
@@ -2086,14 +2086,14 @@
       <c r="R13" s="9">
         <v>46245</v>
       </c>
-      <c r="S13" s="7" t="s">
-        <v>46</v>
+      <c r="S13" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T13" s="10">
         <v>0</v>
       </c>
       <c r="U13" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46246.17149491898</v>
+        <v>46247.204976678244</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2149,14 +2149,14 @@
       <c r="R14" s="5">
         <v>46245</v>
       </c>
-      <c r="S14" s="7" t="s">
-        <v>46</v>
+      <c r="S14" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T14" s="6">
         <v>0</v>
       </c>
       <c r="U14" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46246.17326760417</v>
+        <v>46247.20497568287</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>65</v>
@@ -2212,14 +2212,14 @@
       <c r="R15" s="9">
         <v>46245</v>
       </c>
-      <c r="S15" s="7" t="s">
-        <v>46</v>
+      <c r="S15" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T15" s="10">
         <v>0</v>
       </c>
       <c r="U15" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -2323,7 +2323,7 @@
         <v>46247</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>68</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>75</v>
@@ -2386,7 +2386,7 @@
         <v>46248</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>68</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>78</v>
@@ -2449,7 +2449,7 @@
         <v>46248</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>46309</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         <v>46251</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>46252</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>46252</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>46311</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
@@ -3451,7 +3451,7 @@
         <v>46251</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
@@ -3567,7 +3567,7 @@
         <v>46288</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
@@ -3683,7 +3683,7 @@
         <v>46308</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
@@ -3799,7 +3799,7 @@
         <v>46379</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>46247</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>46247</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4353,7 +4353,7 @@
         <v>46247</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4522,7 +4522,7 @@
         <v>46352</v>
       </c>
       <c r="S56" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>46248</v>
       </c>
       <c r="S58" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -4801,7 +4801,7 @@
         <v>46251</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
@@ -4970,7 +4970,7 @@
         <v>46248</v>
       </c>
       <c r="S64" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5139,7 +5139,7 @@
         <v>46374</v>
       </c>
       <c r="S67" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5308,7 +5308,7 @@
         <v>46377</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
@@ -5477,7 +5477,7 @@
         <v>46378</v>
       </c>
       <c r="S73" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
@@ -5646,7 +5646,7 @@
         <v>46384</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
@@ -5862,7 +5862,7 @@
         <v>46385</v>
       </c>
       <c r="S80" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
@@ -6031,7 +6031,7 @@
         <v>46386</v>
       </c>
       <c r="S83" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T83" s="10">
         <v>0</v>
@@ -6200,7 +6200,7 @@
         <v>46391</v>
       </c>
       <c r="S86" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
@@ -6369,7 +6369,7 @@
         <v>46392</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
@@ -6585,7 +6585,7 @@
         <v>46393</v>
       </c>
       <c r="S93" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T93" s="10">
         <v>0</v>
@@ -6648,7 +6648,7 @@
         <v>46393</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -223,13 +223,13 @@
     <t>Propuesta Alabes ot 4387,Propuesta rodete ot 4387</t>
   </si>
   <si>
+    <t>1217118826927689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF,Ingenieria Jefe de proyecto:,Plano Preliminar   ot 4387  </t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>1217118826927689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF,Ingenieria Jefe de proyecto:,Plano Preliminar   ot 4387  </t>
   </si>
   <si>
     <t>1217117619809504</t>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46247.17175421296</v>
+        <v>46248.17733828704</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1913,8 +1913,8 @@
       <c r="R10" s="5">
         <v>46245</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>50</v>
+      <c r="S10" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T10" s="6">
         <v>0</v>
@@ -1925,14 +1925,14 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="9">
         <v>46237.567974537036</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46245.748681655095</v>
+        <v>46248.172756354164</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>42</v>
@@ -1968,7 +1968,7 @@
         <v>38</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q11" s="9">
         <v>46248</v>
@@ -1977,7 +1977,7 @@
         <v>46245</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T11" s="10">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46244.626402326394</v>
+        <v>46248.17275884259</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>45</v>
@@ -2323,7 +2323,7 @@
         <v>46247</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>46248</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>46248</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>46309</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         <v>46251</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>46252</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>46252</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>46311</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
@@ -3451,7 +3451,7 @@
         <v>46251</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
@@ -3567,7 +3567,7 @@
         <v>46288</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
@@ -3683,7 +3683,7 @@
         <v>46308</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
@@ -3799,7 +3799,7 @@
         <v>46379</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>46247</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46244.62757822916</v>
+        <v>46248.174775520834</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>171</v>
@@ -4184,7 +4184,7 @@
         <v>46247</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46244.62767627314</v>
+        <v>46248.17477728009</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>141</v>
@@ -4353,7 +4353,7 @@
         <v>46247</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46244.627803055555</v>
+        <v>46248.174778472225</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>66</v>
@@ -4522,7 +4522,7 @@
         <v>46352</v>
       </c>
       <c r="S56" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>46248</v>
       </c>
       <c r="S58" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -4801,7 +4801,7 @@
         <v>46251</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
@@ -4970,7 +4970,7 @@
         <v>46248</v>
       </c>
       <c r="S64" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5139,7 +5139,7 @@
         <v>46374</v>
       </c>
       <c r="S67" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5308,7 +5308,7 @@
         <v>46377</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
@@ -5477,7 +5477,7 @@
         <v>46378</v>
       </c>
       <c r="S73" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
@@ -5646,7 +5646,7 @@
         <v>46384</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
@@ -5862,7 +5862,7 @@
         <v>46385</v>
       </c>
       <c r="S80" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
@@ -6031,7 +6031,7 @@
         <v>46386</v>
       </c>
       <c r="S83" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T83" s="10">
         <v>0</v>
@@ -6200,7 +6200,7 @@
         <v>46391</v>
       </c>
       <c r="S86" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
@@ -6369,7 +6369,7 @@
         <v>46392</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
@@ -6585,7 +6585,7 @@
         <v>46393</v>
       </c>
       <c r="S93" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T93" s="10">
         <v>0</v>
@@ -6648,7 +6648,7 @@
         <v>46393</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -229,76 +229,76 @@
     <t xml:space="preserve">ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF,Ingenieria Jefe de proyecto:,Plano Preliminar   ot 4387  </t>
   </si>
   <si>
+    <t>1217117619809504</t>
+  </si>
+  <si>
+    <t>Reservas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva rodete  ot 4387 ,Reserva Alabes ot 4387 </t>
+  </si>
+  <si>
+    <t>1217118826927714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva Alabes ot 4387 </t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Reservas,o 2 4387 -ZVN 1-16-330/4 + TOB + REJ + JF</t>
+  </si>
+  <si>
+    <t>1217119013294914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva rodete  ot 4387 </t>
+  </si>
+  <si>
+    <t>Reservas,ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF</t>
+  </si>
+  <si>
+    <t>1217303610147236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva motor ot 4387 </t>
+  </si>
+  <si>
+    <t>ot2  4387 -ZVN 1-16-330/4 + TOB + REJ + JF</t>
+  </si>
+  <si>
+    <t>1217117619809506</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>Propuesta Motor  ot 4387 ,Propuesta Alabes ot 4387,Propuesta rodete ot 4387</t>
+  </si>
+  <si>
+    <t>1217118826954117</t>
+  </si>
+  <si>
+    <t>Generacion oc  ot 4387,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1217303610147238</t>
+  </si>
+  <si>
+    <t>Propuesta Alabes ot 4387</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC ALABES  ot 4387</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>1217117619809504</t>
-  </si>
-  <si>
-    <t>Reservas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva rodete  ot 4387 ,Reserva Alabes ot 4387 </t>
-  </si>
-  <si>
-    <t>1217118826927714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva Alabes ot 4387 </t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Reservas,o 2 4387 -ZVN 1-16-330/4 + TOB + REJ + JF</t>
-  </si>
-  <si>
-    <t>1217119013294914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva rodete  ot 4387 </t>
-  </si>
-  <si>
-    <t>Reservas,ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF</t>
-  </si>
-  <si>
-    <t>1217303610147236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva motor ot 4387 </t>
-  </si>
-  <si>
-    <t>ot2  4387 -ZVN 1-16-330/4 + TOB + REJ + JF</t>
-  </si>
-  <si>
-    <t>1217117619809506</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>Propuesta Motor  ot 4387 ,Propuesta Alabes ot 4387,Propuesta rodete ot 4387</t>
-  </si>
-  <si>
-    <t>1217118826954117</t>
-  </si>
-  <si>
-    <t>Generacion oc  ot 4387,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1217303610147238</t>
-  </si>
-  <si>
-    <t>Propuesta Alabes ot 4387</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC ALABES  ot 4387</t>
   </si>
   <si>
     <t>1217303610147239</t>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46248.172756354164</v>
+        <v>46249.169830983796</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>42</v>
@@ -1976,8 +1976,8 @@
       <c r="R11" s="9">
         <v>46245</v>
       </c>
-      <c r="S11" s="7" t="s">
-        <v>52</v>
+      <c r="S11" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T11" s="10">
         <v>0</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="5">
         <v>46237.56789387732</v>
@@ -1998,7 +1998,7 @@
         <v>46244.59245125</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>25</v>
@@ -2022,7 +2022,7 @@
         <v>26</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>26</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="9">
         <v>46237.56797914352</v>
@@ -2045,16 +2045,16 @@
         <v>46247.20497636574</v>
       </c>
       <c r="E13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="10" t="s">
+      <c r="H13" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I13" s="9">
         <v>46245</v>
@@ -2072,13 +2072,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O13" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q13" s="9">
         <v>46246</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" s="5">
         <v>46237.56798344907</v>
@@ -2108,16 +2108,16 @@
         <v>46247.204976678244</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I14" s="5">
         <v>46245</v>
@@ -2135,13 +2135,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q14" s="5">
         <v>46246</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" s="9">
         <v>46244.57396097222</v>
@@ -2171,16 +2171,16 @@
         <v>46247.20497568287</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I15" s="9">
         <v>46245</v>
@@ -2198,13 +2198,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q15" s="9">
         <v>46246</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="5">
         <v>46237.567898078705</v>
@@ -2234,7 +2234,7 @@
         <v>46244.59351666667</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -2258,7 +2258,7 @@
         <v>26</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>26</v>
@@ -2271,14 +2271,14 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="9">
         <v>46237.56800255787</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46248.17275884259</v>
+        <v>46249.16983096064</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>45</v>
@@ -2308,13 +2308,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>44</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q17" s="9">
         <v>46248</v>
@@ -2322,19 +2322,19 @@
       <c r="R17" s="9">
         <v>46247</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>52</v>
+      <c r="S17" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5">
         <v>46244.57445940972</v>
@@ -2344,7 +2344,7 @@
         <v>46244.62639877315</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2371,13 +2371,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>48</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="5">
         <v>46251</v>
@@ -2386,13 +2386,13 @@
         <v>46248</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -2413,10 +2413,10 @@
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I19" s="9">
         <v>46248</v>
@@ -2434,7 +2434,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>48</v>
@@ -2449,13 +2449,13 @@
         <v>46248</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -2476,10 +2476,10 @@
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I20" s="5">
         <v>46309</v>
@@ -2497,7 +2497,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>81</v>
@@ -2512,13 +2512,13 @@
         <v>46309</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -2622,13 +2622,13 @@
         <v>46251</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2844,13 +2844,13 @@
         <v>46252</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -2895,7 +2895,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>104</v>
@@ -3013,13 +3013,13 @@
         <v>46252</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3182,13 +3182,13 @@
         <v>46311</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3451,13 +3451,13 @@
         <v>46251</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3567,13 +3567,13 @@
         <v>46288</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3683,13 +3683,13 @@
         <v>46308</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -3799,13 +3799,13 @@
         <v>46379</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -3873,7 +3873,7 @@
         <v>46244.627506226854</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -3903,7 +3903,7 @@
         <v>154</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>141</v>
@@ -4015,13 +4015,13 @@
         <v>46247</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4119,7 +4119,7 @@
         <v>164</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>164</v>
@@ -4184,13 +4184,13 @@
         <v>46247</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4288,7 +4288,7 @@
         <v>173</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>173</v>
@@ -4353,13 +4353,13 @@
         <v>46247</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4427,7 +4427,7 @@
         <v>46248.174778472225</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4457,7 +4457,7 @@
         <v>179</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>179</v>
@@ -4522,13 +4522,13 @@
         <v>46352</v>
       </c>
       <c r="S56" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4596,10 +4596,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4632,13 +4632,13 @@
         <v>46248</v>
       </c>
       <c r="S58" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4659,10 +4659,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I59" s="9">
         <v>46248</v>
@@ -4712,10 +4712,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I60" s="5">
         <v>46342</v>
@@ -4765,10 +4765,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I61" s="9">
         <v>46251</v>
@@ -4801,13 +4801,13 @@
         <v>46251</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -4828,10 +4828,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I62" s="5">
         <v>46251</v>
@@ -4881,10 +4881,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I63" s="9">
         <v>46339</v>
@@ -4934,10 +4934,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I64" s="5">
         <v>46248</v>
@@ -4970,13 +4970,13 @@
         <v>46248</v>
       </c>
       <c r="S64" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -4997,10 +4997,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I65" s="9">
         <v>46248</v>
@@ -5050,10 +5050,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I66" s="5">
         <v>46372</v>
@@ -5103,10 +5103,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I67" s="9">
         <v>46374</v>
@@ -5139,13 +5139,13 @@
         <v>46374</v>
       </c>
       <c r="S67" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5166,10 +5166,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I68" s="5">
         <v>46374</v>
@@ -5219,10 +5219,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I69" s="9">
         <v>46374</v>
@@ -5272,10 +5272,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I70" s="5">
         <v>46377</v>
@@ -5308,13 +5308,13 @@
         <v>46377</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5441,10 +5441,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I73" s="9">
         <v>46378</v>
@@ -5477,13 +5477,13 @@
         <v>46378</v>
       </c>
       <c r="S73" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5504,10 +5504,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I74" s="5">
         <v>46378</v>
@@ -5551,16 +5551,16 @@
         <v>46244.628630057865</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I75" s="9">
         <v>46378</v>
@@ -5610,10 +5610,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I76" s="5">
         <v>46384</v>
@@ -5646,13 +5646,13 @@
         <v>46384</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -5673,10 +5673,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I77" s="9">
         <v>46384</v>
@@ -5726,10 +5726,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I78" s="5">
         <v>46384</v>
@@ -5750,7 +5750,7 @@
         <v>227</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>229</v>
@@ -5862,13 +5862,13 @@
         <v>46385</v>
       </c>
       <c r="S80" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -5995,10 +5995,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I83" s="9">
         <v>46386</v>
@@ -6031,13 +6031,13 @@
         <v>46386</v>
       </c>
       <c r="S83" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T83" s="10">
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6058,10 +6058,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I84" s="5">
         <v>46386</v>
@@ -6111,10 +6111,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="I85" s="9">
         <v>46386</v>
@@ -6200,13 +6200,13 @@
         <v>46391</v>
       </c>
       <c r="S86" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6369,13 +6369,13 @@
         <v>46392</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6585,13 +6585,13 @@
         <v>46393</v>
       </c>
       <c r="S93" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T93" s="10">
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -6648,13 +6648,13 @@
         <v>46393</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -2341,7 +2341,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46244.62639877315</v>
+        <v>46251.17251311343</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46244.626467118054</v>
+        <v>46251.17251584491</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>77</v>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46244.628263819446</v>
+        <v>46251.171475034724</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>141</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -3363,7 +3363,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46244.62259569444</v>
+        <v>46252.606190439816</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>132</v>
@@ -3408,9 +3408,11 @@
       <c r="B37" s="9">
         <v>46237.568062604165</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="9">
+        <v>46252.60617233797</v>
+      </c>
       <c r="D37" s="9">
-        <v>46252.55381060185</v>
+        <v>46252.60659574074</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>135</v>
@@ -3458,10 +3460,10 @@
         <v>82</v>
       </c>
       <c r="T37" s="10">
-        <v>0</v>
-      </c>
-      <c r="U37" s="11" t="s">
-        <v>71</v>
+        <v>1</v>
+      </c>
+      <c r="U37" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3471,9 +3473,11 @@
       <c r="B38" s="5">
         <v>46237.568067395834</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46252.60615847222</v>
+      </c>
       <c r="D38" s="5">
-        <v>46252.55354868056</v>
+        <v>46252.60616018518</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3526,7 +3530,7 @@
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46244.73946619213</v>
+        <v>46252.60618912037</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>145</v>
@@ -3589,7 +3593,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46244.6273140625</v>
+        <v>46252.60618966435</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>141</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -2866,7 +2866,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46244.6267512037</v>
+        <v>46253.17107913195</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>103</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46244.62681570602</v>
+        <v>46253.17108223379</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46252.606190439816</v>
+        <v>46252.98552126157</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>132</v>
@@ -3528,9 +3528,11 @@
       <c r="B39" s="9">
         <v>46237.5680733912</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46252.98551134259</v>
+      </c>
       <c r="D39" s="9">
-        <v>46252.60618912037</v>
+        <v>46252.98552480324</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>145</v>
@@ -3578,10 +3580,10 @@
         <v>82</v>
       </c>
       <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>71</v>
+        <v>1</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3591,9 +3593,11 @@
       <c r="B40" s="5">
         <v>46237.56807820602</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46252.98549689815</v>
+      </c>
       <c r="D40" s="5">
-        <v>46252.60618966435</v>
+        <v>46252.98549872685</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>141</v>
@@ -3646,7 +3650,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46244.62720873843</v>
+        <v>46252.98552188657</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>80</v>
@@ -3709,7 +3713,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46244.62736225694</v>
+        <v>46252.98552255787</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>141</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="273">
   <si>
     <t>50001586 - "ZITRON PERU SAC  CONDESTABLE"</t>
   </si>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>generacion componentes  oc rodetes  ot 4387,fabricacion componentes  rodete   ot 4387</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1217303695864936</t>
@@ -2972,7 +2975,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46244.626611886575</v>
+        <v>46255.188699085644</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>109</v>
@@ -3016,8 +3019,8 @@
       <c r="R29" s="9">
         <v>46252</v>
       </c>
-      <c r="S29" s="7" t="s">
-        <v>82</v>
+      <c r="S29" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
@@ -3028,7 +3031,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5">
         <v>46244.576040555556</v>
@@ -3038,7 +3041,7 @@
         <v>46253.17108223379</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3071,7 +3074,7 @@
         <v>76</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3081,7 +3084,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B31" s="9">
         <v>46244.57612224537</v>
@@ -3091,7 +3094,7 @@
         <v>46244.626811469905</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3121,10 +3124,10 @@
         <v>109</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3134,7 +3137,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46237.56803458333</v>
@@ -3144,16 +3147,16 @@
         <v>46244.62703744213</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I32" s="5">
         <v>46311</v>
@@ -3174,7 +3177,7 @@
         <v>84</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>84</v>
@@ -3197,7 +3200,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B33" s="9">
         <v>46237.56803793981</v>
@@ -3213,10 +3216,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I33" s="9">
         <v>46311</v>
@@ -3234,13 +3237,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3250,7 +3253,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46237.56804157408</v>
@@ -3260,16 +3263,16 @@
         <v>46244.6268963426</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I34" s="5">
         <v>46322</v>
@@ -3287,13 +3290,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3303,7 +3306,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="9">
         <v>46237.56804478009</v>
@@ -3313,16 +3316,16 @@
         <v>46244.62695140047</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I35" s="9">
         <v>46351</v>
@@ -3340,13 +3343,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3356,7 +3359,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46237.568059467594</v>
@@ -3366,7 +3369,7 @@
         <v>46252.98552126157</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>25</v>
@@ -3390,7 +3393,7 @@
         <v>26</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3403,7 +3406,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="9">
         <v>46237.568062604165</v>
@@ -3415,16 +3418,16 @@
         <v>46252.60659574074</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46251</v>
@@ -3442,13 +3445,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9">
         <v>46268</v>
@@ -3468,7 +3471,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46237.568067395834</v>
@@ -3480,16 +3483,16 @@
         <v>46252.60616018518</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I38" s="5">
         <v>46251</v>
@@ -3507,13 +3510,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>42</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3523,7 +3526,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46237.5680733912</v>
@@ -3535,16 +3538,16 @@
         <v>46252.98552480324</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I39" s="9">
         <v>46288</v>
@@ -3562,13 +3565,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q39" s="9">
         <v>46307</v>
@@ -3588,7 +3591,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46237.56807820602</v>
@@ -3600,16 +3603,16 @@
         <v>46252.98549872685</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I40" s="5">
         <v>46288</v>
@@ -3627,13 +3630,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3643,7 +3646,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="9">
         <v>46237.56808336805</v>
@@ -3659,10 +3662,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I41" s="9">
         <v>46308</v>
@@ -3680,13 +3683,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="9">
         <v>46308</v>
@@ -3706,7 +3709,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46237.568094560185</v>
@@ -3716,16 +3719,16 @@
         <v>46252.98552255787</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I42" s="5">
         <v>46308</v>
@@ -3746,7 +3749,7 @@
         <v>80</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>80</v>
@@ -3759,7 +3762,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B43" s="9">
         <v>46237.56809997685</v>
@@ -3769,16 +3772,16 @@
         <v>46244.62740439815</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I43" s="9">
         <v>46379</v>
@@ -3796,13 +3799,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q43" s="9">
         <v>46379</v>
@@ -3822,7 +3825,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46237.56810440972</v>
@@ -3832,16 +3835,16 @@
         <v>46244.62751363426</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I44" s="5">
         <v>46379</v>
@@ -3859,13 +3862,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -3875,7 +3878,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" s="9">
         <v>46244.59380686343</v>
@@ -3891,10 +3894,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I45" s="9">
         <v>46379</v>
@@ -3912,13 +3915,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>65</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -3928,7 +3931,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46237.568445833334</v>
@@ -3938,7 +3941,7 @@
         <v>46244.60831364583</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -3962,7 +3965,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -3975,7 +3978,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B47" s="9">
         <v>46237.568449722225</v>
@@ -3985,16 +3988,16 @@
         <v>46244.62761877315</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I47" s="9">
         <v>46247</v>
@@ -4012,13 +4015,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="9">
         <v>46338</v>
@@ -4038,7 +4041,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46244.60138324074</v>
@@ -4048,16 +4051,16 @@
         <v>46244.627581712964</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I48" s="5">
         <v>46337</v>
@@ -4075,13 +4078,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4091,7 +4094,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B49" s="9">
         <v>46244.60147203704</v>
@@ -4101,16 +4104,16 @@
         <v>46248.174775520834</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I49" s="9">
         <v>46247</v>
@@ -4128,13 +4131,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4144,7 +4147,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B50" s="5">
         <v>46237.568459965274</v>
@@ -4154,16 +4157,16 @@
         <v>46244.62771695602</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I50" s="5">
         <v>46247</v>
@@ -4181,13 +4184,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4207,7 +4210,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B51" s="9">
         <v>46244.601417708334</v>
@@ -4217,16 +4220,16 @@
         <v>46244.62768068287</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I51" s="9">
         <v>46265</v>
@@ -4244,13 +4247,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4260,7 +4263,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B52" s="5">
         <v>46244.60150188657</v>
@@ -4270,16 +4273,16 @@
         <v>46248.17477728009</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I52" s="5">
         <v>46247</v>
@@ -4297,13 +4300,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>61</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4313,7 +4316,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B53" s="9">
         <v>46237.568466979166</v>
@@ -4323,16 +4326,16 @@
         <v>46244.62774751158</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I53" s="9">
         <v>46247</v>
@@ -4350,13 +4353,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q53" s="9">
         <v>46371</v>
@@ -4376,7 +4379,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B54" s="5">
         <v>46244.60144362268</v>
@@ -4386,16 +4389,16 @@
         <v>46244.62780613426</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I54" s="5">
         <v>46370</v>
@@ -4413,13 +4416,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4429,7 +4432,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B55" s="9">
         <v>46244.60153101852</v>
@@ -4445,10 +4448,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I55" s="9">
         <v>46247</v>
@@ -4466,13 +4469,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>64</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4482,7 +4485,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B56" s="5">
         <v>46244.60679788195</v>
@@ -4492,16 +4495,16 @@
         <v>46244.62786810185</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I56" s="5">
         <v>46352</v>
@@ -4519,10 +4522,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4545,7 +4548,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B57" s="9">
         <v>46237.568475821754</v>
@@ -4555,7 +4558,7 @@
         <v>46244.61656334491</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4579,7 +4582,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4592,7 +4595,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B58" s="5">
         <v>46237.56847953703</v>
@@ -4602,7 +4605,7 @@
         <v>46244.62806383102</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4629,13 +4632,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q58" s="5">
         <v>46359</v>
@@ -4655,7 +4658,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B59" s="9">
         <v>46237.56848447917</v>
@@ -4665,7 +4668,7 @@
         <v>46244.6280275926</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4692,13 +4695,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4708,7 +4711,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B60" s="5">
         <v>46237.56848827546</v>
@@ -4718,7 +4721,7 @@
         <v>46244.62802399306</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4745,13 +4748,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4761,7 +4764,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B61" s="9">
         <v>46237.56852555556</v>
@@ -4771,7 +4774,7 @@
         <v>46244.62816917824</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -4798,13 +4801,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q61" s="9">
         <v>46342</v>
@@ -4824,7 +4827,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B62" s="5">
         <v>46237.56853045139</v>
@@ -4834,7 +4837,7 @@
         <v>46252.17020165509</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -4861,13 +4864,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -4877,7 +4880,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B63" s="9">
         <v>46237.56853582176</v>
@@ -4887,7 +4890,7 @@
         <v>46244.62814572916</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -4914,13 +4917,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -4930,7 +4933,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B64" s="5">
         <v>46237.56863671297</v>
@@ -4940,7 +4943,7 @@
         <v>46244.62831047454</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -4967,13 +4970,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q64" s="5">
         <v>46373</v>
@@ -4993,7 +4996,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B65" s="9">
         <v>46237.5686419213</v>
@@ -5003,7 +5006,7 @@
         <v>46251.171475034724</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5030,13 +5033,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5046,7 +5049,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B66" s="5">
         <v>46237.56864618056</v>
@@ -5056,7 +5059,7 @@
         <v>46244.62826003472</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5083,13 +5086,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5099,7 +5102,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B67" s="9">
         <v>46237.568688796295</v>
@@ -5109,7 +5112,7 @@
         <v>46244.628418622684</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5136,13 +5139,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q67" s="9">
         <v>46374</v>
@@ -5162,7 +5165,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B68" s="5">
         <v>46237.568694120375</v>
@@ -5172,7 +5175,7 @@
         <v>46244.628406550924</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5199,13 +5202,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5215,7 +5218,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B69" s="9">
         <v>46237.5686980787</v>
@@ -5225,7 +5228,7 @@
         <v>46244.62839778935</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5252,13 +5255,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5268,7 +5271,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B70" s="5">
         <v>46237.5687887963</v>
@@ -5278,7 +5281,7 @@
         <v>46244.62847181713</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5305,13 +5308,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q70" s="5">
         <v>46377</v>
@@ -5331,7 +5334,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B71" s="9">
         <v>46237.56879706019</v>
@@ -5341,16 +5344,16 @@
         <v>46244.62853349537</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I71" s="9">
         <v>46377</v>
@@ -5368,13 +5371,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5384,7 +5387,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B72" s="5">
         <v>46237.56880100694</v>
@@ -5394,16 +5397,16 @@
         <v>46244.62852962963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I72" s="5">
         <v>46377</v>
@@ -5421,13 +5424,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5437,7 +5440,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B73" s="9">
         <v>46237.56883909722</v>
@@ -5447,7 +5450,7 @@
         <v>46244.6286615162</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5474,10 +5477,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5500,7 +5503,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B74" s="5">
         <v>46237.56884354167</v>
@@ -5510,7 +5513,7 @@
         <v>46244.62863414352</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5537,13 +5540,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5553,7 +5556,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B75" s="9">
         <v>46237.56884784722</v>
@@ -5590,13 +5593,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5606,7 +5609,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B76" s="5">
         <v>46237.56889393518</v>
@@ -5616,7 +5619,7 @@
         <v>46244.62875729166</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5643,10 +5646,10 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5669,7 +5672,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B77" s="9">
         <v>46237.56889887732</v>
@@ -5679,7 +5682,7 @@
         <v>46244.62873818287</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5706,13 +5709,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5722,7 +5725,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B78" s="5">
         <v>46237.568903437495</v>
@@ -5732,7 +5735,7 @@
         <v>46244.62873405093</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5759,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5775,7 +5778,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B79" s="9">
         <v>46237.56899291667</v>
@@ -5785,7 +5788,7 @@
         <v>46244.624352893516</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -5809,7 +5812,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -5822,7 +5825,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B80" s="5">
         <v>46237.568996898146</v>
@@ -5832,16 +5835,16 @@
         <v>46244.6288791088</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I80" s="5">
         <v>46385</v>
@@ -5859,13 +5862,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q80" s="5">
         <v>46385</v>
@@ -5885,7 +5888,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B81" s="9">
         <v>46237.5690024537</v>
@@ -5895,16 +5898,16 @@
         <v>46244.629229375</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I81" s="9">
         <v>46385</v>
@@ -5922,13 +5925,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -5938,7 +5941,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B82" s="5">
         <v>46237.56900662037</v>
@@ -5948,16 +5951,16 @@
         <v>46244.62922577546</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I82" s="5">
         <v>46385</v>
@@ -5975,13 +5978,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -5991,7 +5994,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B83" s="9">
         <v>46237.56904663194</v>
@@ -6001,7 +6004,7 @@
         <v>46244.62915252315</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6028,10 +6031,10 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6054,7 +6057,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B84" s="5">
         <v>46237.56905172454</v>
@@ -6064,7 +6067,7 @@
         <v>46244.62902597222</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6091,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6107,7 +6110,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B85" s="9">
         <v>46237.56905527778</v>
@@ -6117,7 +6120,7 @@
         <v>46244.629022002315</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6144,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6160,7 +6163,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B86" s="5">
         <v>46237.569091666664</v>
@@ -6170,16 +6173,16 @@
         <v>46244.629364050925</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I86" s="5">
         <v>46391</v>
@@ -6197,13 +6200,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q86" s="5">
         <v>46391</v>
@@ -6223,7 +6226,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B87" s="9">
         <v>46237.56913631945</v>
@@ -6233,16 +6236,16 @@
         <v>46244.62929709491</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I87" s="9">
         <v>46391</v>
@@ -6260,13 +6263,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6276,7 +6279,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B88" s="5">
         <v>46237.5691418287</v>
@@ -6286,16 +6289,16 @@
         <v>46244.62929322917</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I88" s="5">
         <v>46391</v>
@@ -6313,13 +6316,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6329,7 +6332,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B89" s="9">
         <v>46237.569190208334</v>
@@ -6339,16 +6342,16 @@
         <v>46244.629517615744</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I89" s="9">
         <v>46392</v>
@@ -6366,13 +6369,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q89" s="9">
         <v>46392</v>
@@ -6392,7 +6395,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B90" s="5">
         <v>46237.56919672454</v>
@@ -6402,16 +6405,16 @@
         <v>46244.62945129629</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I90" s="5">
         <v>46392</v>
@@ -6429,13 +6432,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6445,7 +6448,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B91" s="9">
         <v>46237.5692003588</v>
@@ -6455,16 +6458,16 @@
         <v>46244.62944737269</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I91" s="9">
         <v>46392</v>
@@ -6482,13 +6485,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6498,7 +6501,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B92" s="5">
         <v>46237.569236180556</v>
@@ -6508,7 +6511,7 @@
         <v>46244.62474721065</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -6532,7 +6535,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -6545,7 +6548,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B93" s="9">
         <v>46237.56923991899</v>
@@ -6555,16 +6558,16 @@
         <v>46244.629587233794</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I93" s="9">
         <v>46393</v>
@@ -6582,13 +6585,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q93" s="9">
         <v>46401</v>
@@ -6608,7 +6611,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B94" s="5">
         <v>46237.569245810184</v>
@@ -6618,16 +6621,16 @@
         <v>46244.62958366898</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I94" s="5">
         <v>46393</v>
@@ -6645,13 +6648,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q94" s="5">
         <v>46401</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -4154,7 +4154,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46244.62771695602</v>
+        <v>46259.2006631713</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>174</v>
@@ -4198,8 +4198,8 @@
       <c r="R50" s="5">
         <v>46247</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>82</v>
+      <c r="S50" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -202,57 +202,57 @@
     <t>Ingenieria Detalle  ot 4387</t>
   </si>
   <si>
+    <t>1217118826919313</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Motor ot 4387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Motor  ot 4387 </t>
+  </si>
+  <si>
+    <t>1217303695864968</t>
+  </si>
+  <si>
+    <t>Ingenieria basica nucleo rodete   ot 4387</t>
+  </si>
+  <si>
+    <t>Propuesta Alabes ot 4387,Propuesta rodete ot 4387</t>
+  </si>
+  <si>
+    <t>1217118826927689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF,Ingenieria Jefe de proyecto:,Plano Preliminar   ot 4387  </t>
+  </si>
+  <si>
+    <t>1217117619809504</t>
+  </si>
+  <si>
+    <t>Reservas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva rodete  ot 4387 ,Reserva Alabes ot 4387 </t>
+  </si>
+  <si>
+    <t>1217118826927714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva Alabes ot 4387 </t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Reservas,o 2 4387 -ZVN 1-16-330/4 + TOB + REJ + JF</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1217118826919313</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Motor ot 4387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Motor  ot 4387 </t>
-  </si>
-  <si>
-    <t>1217303695864968</t>
-  </si>
-  <si>
-    <t>Ingenieria basica nucleo rodete   ot 4387</t>
-  </si>
-  <si>
-    <t>Propuesta Alabes ot 4387,Propuesta rodete ot 4387</t>
-  </si>
-  <si>
-    <t>1217118826927689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF,Ingenieria Jefe de proyecto:,Plano Preliminar   ot 4387  </t>
-  </si>
-  <si>
-    <t>1217117619809504</t>
-  </si>
-  <si>
-    <t>Reservas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva rodete  ot 4387 ,Reserva Alabes ot 4387 </t>
-  </si>
-  <si>
-    <t>1217118826927714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva Alabes ot 4387 </t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Reservas,o 2 4387 -ZVN 1-16-330/4 + TOB + REJ + JF</t>
-  </si>
-  <si>
     <t>1217119013294914</t>
   </si>
   <si>
@@ -286,40 +286,40 @@
     <t>Generacion oc  ot 4387,Propuesta compras:</t>
   </si>
   <si>
+    <t>1217303610147238</t>
+  </si>
+  <si>
+    <t>Propuesta Alabes ot 4387</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC ALABES  ot 4387</t>
+  </si>
+  <si>
+    <t>1217303610147239</t>
+  </si>
+  <si>
+    <t>Propuesta rodete ot 4387</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,generacion componentes  oc rodetes  ot 4387</t>
+  </si>
+  <si>
+    <t>1217303695864946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Fabricación externa  ot 4387 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Planos   ot 4387  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion Oc ot 4387 </t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1217303610147238</t>
-  </si>
-  <si>
-    <t>Propuesta Alabes ot 4387</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC ALABES  ot 4387</t>
-  </si>
-  <si>
-    <t>1217303610147239</t>
-  </si>
-  <si>
-    <t>Propuesta rodete ot 4387</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,generacion componentes  oc rodetes  ot 4387</t>
-  </si>
-  <si>
-    <t>1217303695864946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Fabricación externa  ot 4387 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Planos   ot 4387  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion Oc ot 4387 </t>
-  </si>
-  <si>
-    <t>Baja</t>
   </si>
   <si>
     <t>1217117619809508</t>
@@ -1760,9 +1760,11 @@
       <c r="B8" s="5">
         <v>46237.56788935185</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="5">
+        <v>46259.715407129625</v>
+      </c>
       <c r="D8" s="5">
-        <v>46252.55356030093</v>
+        <v>46259.71541803241</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1797,24 +1799,28 @@
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="12" t="s">
-        <v>43</v>
+      <c r="T8" s="6">
+        <v>1</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="9">
         <v>46237.56797127315</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="9">
+        <v>46259.715388321754</v>
+      </c>
       <c r="D9" s="9">
-        <v>46247.20498152778</v>
+        <v>46259.71540753472</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>26</v>
@@ -1847,7 +1853,7 @@
         <v>38</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q9" s="9">
         <v>46246</v>
@@ -1859,25 +1865,27 @@
         <v>33</v>
       </c>
       <c r="T9" s="10">
-        <v>0</v>
-      </c>
-      <c r="U9" s="12" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="5">
         <v>46244.588363981486</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46259.71539701389</v>
+      </c>
       <c r="D10" s="5">
-        <v>46248.17733828704</v>
+        <v>46259.71541480324</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>26</v>
@@ -1910,7 +1918,7 @@
         <v>38</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q10" s="5">
         <v>46247</v>
@@ -1922,15 +1930,15 @@
         <v>33</v>
       </c>
       <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="12" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="9">
         <v>46237.567974537036</v>
@@ -1975,7 +1983,7 @@
         <v>38</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q11" s="9">
         <v>46248</v>
@@ -1995,7 +2003,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="5">
         <v>46237.56789387732</v>
@@ -2005,7 +2013,7 @@
         <v>46244.59245125</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>25</v>
@@ -2029,7 +2037,7 @@
         <v>26</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>26</v>
@@ -2042,7 +2050,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="9">
         <v>46237.56797914352</v>
@@ -2052,16 +2060,16 @@
         <v>46247.20497636574</v>
       </c>
       <c r="E13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="10" t="s">
+      <c r="H13" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I13" s="9">
         <v>46245</v>
@@ -2079,13 +2087,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O13" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q13" s="9">
         <v>46246</v>
@@ -2100,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="12" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2121,10 +2129,10 @@
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I14" s="5">
         <v>46245</v>
@@ -2142,7 +2150,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>38</v>
@@ -2163,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="U14" s="12" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -2173,9 +2181,11 @@
       <c r="B15" s="9">
         <v>46244.57396097222</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="9">
+        <v>46259.82100844907</v>
+      </c>
       <c r="D15" s="9">
-        <v>46247.20497568287</v>
+        <v>46259.82102393519</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2184,10 +2194,10 @@
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I15" s="9">
         <v>46245</v>
@@ -2205,7 +2215,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>38</v>
@@ -2223,10 +2233,10 @@
         <v>33</v>
       </c>
       <c r="T15" s="10">
-        <v>0</v>
-      </c>
-      <c r="U15" s="12" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -2285,10 +2295,10 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46249.16983096064</v>
+        <v>46259.71540726852</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2318,7 +2328,7 @@
         <v>67</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P17" s="10" t="s">
         <v>70</v>
@@ -2335,23 +2345,23 @@
       <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="11" t="s">
-        <v>71</v>
+      <c r="U17" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5">
         <v>46244.57445940972</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46252.20071665509</v>
+        <v>46259.715414085644</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2381,10 +2391,10 @@
         <v>67</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q18" s="5">
         <v>46251</v>
@@ -2398,32 +2408,32 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="11" t="s">
-        <v>71</v>
+      <c r="U18" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B19" s="9">
         <v>46244.574642708336</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46252.20071686343</v>
+        <v>46259.715415162034</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I19" s="9">
         <v>46248</v>
@@ -2444,10 +2454,10 @@
         <v>67</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="9">
         <v>46251</v>
@@ -2461,13 +2471,13 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="11" t="s">
-        <v>71</v>
+      <c r="U19" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20" s="5">
         <v>46244.57978112268</v>
@@ -2477,16 +2487,16 @@
         <v>46244.62653376158</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I20" s="5">
         <v>46309</v>
@@ -2507,10 +2517,10 @@
         <v>67</v>
       </c>
       <c r="O20" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P20" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="Q20" s="5">
         <v>46310</v>
@@ -2519,13 +2529,13 @@
         <v>46309</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -2629,13 +2639,13 @@
         <v>46251</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2680,7 +2690,7 @@
         <v>87</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>93</v>
@@ -2851,13 +2861,13 @@
         <v>46252</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -2902,7 +2912,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>104</v>
@@ -3026,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3071,7 +3081,7 @@
         <v>109</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>114</v>
@@ -3189,13 +3199,13 @@
         <v>46311</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3210,7 +3220,7 @@
         <v>46244.62690074074</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3240,7 +3250,7 @@
         <v>119</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>124</v>
@@ -3293,7 +3303,7 @@
         <v>119</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>127</v>
@@ -3460,7 +3470,7 @@
         <v>46251</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T37" s="10">
         <v>1</v>
@@ -3580,7 +3590,7 @@
         <v>46288</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3656,7 +3666,7 @@
         <v>46252.98552188657</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -3698,13 +3708,13 @@
         <v>46308</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -3746,13 +3756,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3814,13 +3824,13 @@
         <v>46379</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4030,13 +4040,13 @@
         <v>46247</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4134,7 +4144,7 @@
         <v>165</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>165</v>
@@ -4205,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4368,13 +4378,13 @@
         <v>46247</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4439,7 +4449,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46248.174778472225</v>
+        <v>46259.82101358796</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>65</v>
@@ -4537,13 +4547,13 @@
         <v>46352</v>
       </c>
       <c r="S56" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4611,10 +4621,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4647,13 +4657,13 @@
         <v>46248</v>
       </c>
       <c r="S58" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4674,10 +4684,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I59" s="9">
         <v>46248</v>
@@ -4727,10 +4737,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I60" s="5">
         <v>46342</v>
@@ -4780,10 +4790,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I61" s="9">
         <v>46251</v>
@@ -4816,13 +4826,13 @@
         <v>46251</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -4843,10 +4853,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I62" s="5">
         <v>46251</v>
@@ -4896,10 +4906,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I63" s="9">
         <v>46339</v>
@@ -4949,10 +4959,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I64" s="5">
         <v>46248</v>
@@ -4985,13 +4995,13 @@
         <v>46248</v>
       </c>
       <c r="S64" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5012,10 +5022,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I65" s="9">
         <v>46248</v>
@@ -5065,10 +5075,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I66" s="5">
         <v>46372</v>
@@ -5118,10 +5128,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I67" s="9">
         <v>46374</v>
@@ -5154,13 +5164,13 @@
         <v>46374</v>
       </c>
       <c r="S67" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5181,10 +5191,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I68" s="5">
         <v>46374</v>
@@ -5234,10 +5244,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I69" s="9">
         <v>46374</v>
@@ -5287,10 +5297,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I70" s="5">
         <v>46377</v>
@@ -5323,13 +5333,13 @@
         <v>46377</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5456,10 +5466,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I73" s="9">
         <v>46378</v>
@@ -5492,13 +5502,13 @@
         <v>46378</v>
       </c>
       <c r="S73" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5519,10 +5529,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I74" s="5">
         <v>46378</v>
@@ -5572,10 +5582,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I75" s="9">
         <v>46378</v>
@@ -5625,10 +5635,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I76" s="5">
         <v>46384</v>
@@ -5661,13 +5671,13 @@
         <v>46384</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -5688,10 +5698,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I77" s="9">
         <v>46384</v>
@@ -5741,10 +5751,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I78" s="5">
         <v>46384</v>
@@ -5877,13 +5887,13 @@
         <v>46385</v>
       </c>
       <c r="S80" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6010,10 +6020,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I83" s="9">
         <v>46386</v>
@@ -6046,13 +6056,13 @@
         <v>46386</v>
       </c>
       <c r="S83" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T83" s="10">
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6073,10 +6083,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I84" s="5">
         <v>46386</v>
@@ -6126,10 +6136,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I85" s="9">
         <v>46386</v>
@@ -6215,13 +6225,13 @@
         <v>46391</v>
       </c>
       <c r="S86" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6384,13 +6394,13 @@
         <v>46392</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6600,13 +6610,13 @@
         <v>46393</v>
       </c>
       <c r="S93" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T93" s="10">
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -6663,13 +6673,13 @@
         <v>46393</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="273">
   <si>
     <t>50001586 - "ZITRON PERU SAC  CONDESTABLE"</t>
   </si>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46251.171475034724</v>
+        <v>46260.57276982639</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>142</v>
@@ -5055,7 +5055,9 @@
       <c r="R65" s="10"/>
       <c r="S65" s="10"/>
       <c r="T65" s="10"/>
-      <c r="U65" s="10"/>
+      <c r="U65" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -3425,7 +3425,7 @@
         <v>46252.60617233797</v>
       </c>
       <c r="D37" s="9">
-        <v>46252.60659574074</v>
+        <v>46261.20192975695</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>136</v>
@@ -3469,8 +3469,8 @@
       <c r="R37" s="9">
         <v>46251</v>
       </c>
-      <c r="S37" s="7" t="s">
-        <v>81</v>
+      <c r="S37" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T37" s="10">
         <v>1</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46255.188699085644</v>
+        <v>46262.17184563658</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>109</v>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46244.626811469905</v>
+        <v>46262.17184758102</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>116</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -406,94 +406,94 @@
     <t>generacion componentes  oc rodetes  ot 4387,fabricacion componentes  rodete   ot 4387</t>
   </si>
   <si>
+    <t>1217303695864936</t>
+  </si>
+  <si>
+    <t>generacion componentes  oc rodetes  ot 4387</t>
+  </si>
+  <si>
+    <t>fabricacion componentes  rodete   ot 4387,Rodetes ot 4387</t>
+  </si>
+  <si>
+    <t>1217303695864937</t>
+  </si>
+  <si>
+    <t>fabricacion componentes  rodete   ot 4387</t>
+  </si>
+  <si>
+    <t>Rodetes ot 4387,ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF</t>
+  </si>
+  <si>
+    <t>1217118826978519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa    ot 4387    </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado  OT ot 4387 ,Control de calidad   ot 4387 ,Generacion Oc ot 4387 </t>
+  </si>
+  <si>
+    <t>1217118823569091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa    ot 4387    ,Armado  OT ot 4387 </t>
+  </si>
+  <si>
+    <t>1217118823569109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado  OT ot 4387 </t>
+  </si>
+  <si>
+    <t>Fabricación externa    ot 4387    ,Control de calidad   ot 4387 ,Recepcion fabricación externa   ot 4387</t>
+  </si>
+  <si>
+    <t>1217118795808394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad   ot 4387 </t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1217118910805453</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Definitivos   ot 4387   ,Check Planos   ot 4387  ,Plano Preliminar   ot 4387  ,Check pruebas FAT  ot 4387   </t>
+  </si>
+  <si>
+    <t>1217119013379724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Preliminar   ot 4387  </t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF,Ingenieria Detalle  ot 4387</t>
+  </si>
+  <si>
+    <t>Plano Definitivos   ot 4387   ,ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF,Ingenieria y diseño:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1217303695864936</t>
-  </si>
-  <si>
-    <t>generacion componentes  oc rodetes  ot 4387</t>
-  </si>
-  <si>
-    <t>fabricacion componentes  rodete   ot 4387,Rodetes ot 4387</t>
-  </si>
-  <si>
-    <t>1217303695864937</t>
-  </si>
-  <si>
-    <t>fabricacion componentes  rodete   ot 4387</t>
-  </si>
-  <si>
-    <t>Rodetes ot 4387,ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF</t>
-  </si>
-  <si>
-    <t>1217118826978519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa    ot 4387    </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado  OT ot 4387 ,Control de calidad   ot 4387 ,Generacion Oc ot 4387 </t>
-  </si>
-  <si>
-    <t>1217118823569091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa    ot 4387    ,Armado  OT ot 4387 </t>
-  </si>
-  <si>
-    <t>1217118823569109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado  OT ot 4387 </t>
-  </si>
-  <si>
-    <t>Fabricación externa    ot 4387    ,Control de calidad   ot 4387 ,Recepcion fabricación externa   ot 4387</t>
-  </si>
-  <si>
-    <t>1217118795808394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad   ot 4387 </t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1217118910805453</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Definitivos   ot 4387   ,Check Planos   ot 4387  ,Plano Preliminar   ot 4387  ,Check pruebas FAT  ot 4387   </t>
-  </si>
-  <si>
-    <t>1217119013379724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Preliminar   ot 4387  </t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF,Ingenieria Detalle  ot 4387</t>
-  </si>
-  <si>
-    <t>Plano Definitivos   ot 4387   ,ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF,Ingenieria y diseño:</t>
   </si>
   <si>
     <t>1217119013379747</t>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46262.17184563658</v>
+        <v>46263.17857559028</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>109</v>
@@ -3029,8 +3029,8 @@
       <c r="R29" s="9">
         <v>46252</v>
       </c>
-      <c r="S29" s="12" t="s">
-        <v>111</v>
+      <c r="S29" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B30" s="5">
         <v>46244.576040555556</v>
@@ -3051,7 +3051,7 @@
         <v>46253.17108223379</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3084,7 +3084,7 @@
         <v>75</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B31" s="9">
         <v>46244.57612224537</v>
@@ -3104,7 +3104,7 @@
         <v>46262.17184758102</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3134,10 +3134,10 @@
         <v>109</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3147,7 +3147,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46237.56803458333</v>
@@ -3157,16 +3157,16 @@
         <v>46244.62703744213</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="I32" s="5">
         <v>46311</v>
@@ -3187,7 +3187,7 @@
         <v>84</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>84</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B33" s="9">
         <v>46237.56803793981</v>
@@ -3226,10 +3226,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="I33" s="9">
         <v>46311</v>
@@ -3247,13 +3247,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>78</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46237.56804157408</v>
@@ -3273,16 +3273,16 @@
         <v>46244.6268963426</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="I34" s="5">
         <v>46322</v>
@@ -3300,13 +3300,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>80</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" s="9">
         <v>46237.56804478009</v>
@@ -3326,16 +3326,16 @@
         <v>46244.62695140047</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="I35" s="9">
         <v>46351</v>
@@ -3353,13 +3353,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46237.568059467594</v>
@@ -3379,7 +3379,7 @@
         <v>46252.98552126157</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>25</v>
@@ -3403,7 +3403,7 @@
         <v>26</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="9">
         <v>46237.568062604165</v>
@@ -3428,16 +3428,16 @@
         <v>46261.20192975695</v>
       </c>
       <c r="E37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="10" t="s">
+      <c r="H37" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46251</v>
@@ -3455,13 +3455,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O37" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="P37" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="Q37" s="9">
         <v>46268</v>
@@ -3470,7 +3470,7 @@
         <v>46251</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="T37" s="10">
         <v>1</v>
@@ -3520,13 +3520,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>42</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3554,10 +3554,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I39" s="9">
         <v>46288</v>
@@ -3575,7 +3575,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>147</v>
@@ -3643,7 +3643,7 @@
         <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>146</v>
@@ -3693,7 +3693,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>151</v>
@@ -3809,13 +3809,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>142</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q43" s="9">
         <v>46379</v>
@@ -4209,7 +4209,7 @@
         <v>46247</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4260,7 +4260,7 @@
         <v>174</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>174</v>
@@ -4535,7 +4535,7 @@
         <v>162</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -4164,7 +4164,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46259.2006631713</v>
+        <v>46266.17017809028</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>174</v>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46244.62768068287</v>
+        <v>46266.17098471065</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>142</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -2657,7 +2657,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46244.6266994676</v>
+        <v>46267.16925467593</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>92</v>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46266.17017809028</v>
+        <v>46267.18103443287</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>174</v>
@@ -4208,8 +4208,8 @@
       <c r="R50" s="5">
         <v>46247</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>140</v>
+      <c r="S50" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -4675,7 +4675,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46244.6280275926</v>
+        <v>46268.16902230324</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>142</v>

--- a/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
+++ b/data/50001586 - ZITRON PERU SAC  CONDESTABLE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="272">
   <si>
     <t>50001586 - "ZITRON PERU SAC  CONDESTABLE"</t>
   </si>
@@ -491,9 +491,6 @@
   </si>
   <si>
     <t>Plano Definitivos   ot 4387   ,ot  4387 -ZVN 1-16-330/4 + TOB + REJ + JF,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1217119013379747</t>
@@ -3425,7 +3422,7 @@
         <v>46252.60617233797</v>
       </c>
       <c r="D37" s="9">
-        <v>46261.20192975695</v>
+        <v>46269.18922609954</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>135</v>
@@ -3469,8 +3466,8 @@
       <c r="R37" s="9">
         <v>46251</v>
       </c>
-      <c r="S37" s="12" t="s">
-        <v>140</v>
+      <c r="S37" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T37" s="10">
         <v>1</v>
@@ -3481,7 +3478,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46237.568067395834</v>
@@ -3493,16 +3490,16 @@
         <v>46252.60616018518</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="I38" s="5">
         <v>46251</v>
@@ -3536,7 +3533,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B39" s="9">
         <v>46237.5680733912</v>
@@ -3548,7 +3545,7 @@
         <v>46252.98552480324</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
@@ -3578,10 +3575,10 @@
         <v>132</v>
       </c>
       <c r="O39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="P39" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="P39" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="Q39" s="9">
         <v>46307</v>
@@ -3601,7 +3598,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46237.56807820602</v>
@@ -3613,16 +3610,16 @@
         <v>46252.98549872685</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="I40" s="5">
         <v>46288</v>
@@ -3640,13 +3637,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>135</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3656,7 +3653,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B41" s="9">
         <v>46237.56808336805</v>
@@ -3672,10 +3669,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="I41" s="9">
         <v>46308</v>
@@ -3696,10 +3693,10 @@
         <v>132</v>
       </c>
       <c r="O41" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="P41" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="P41" s="10" t="s">
-        <v>152</v>
       </c>
       <c r="Q41" s="9">
         <v>46308</v>
@@ -3719,7 +3716,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46237.568094560185</v>
@@ -3729,16 +3726,16 @@
         <v>46252.98552255787</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="I42" s="5">
         <v>46308</v>
@@ -3759,7 +3756,7 @@
         <v>79</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>79</v>
@@ -3772,7 +3769,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B43" s="9">
         <v>46237.56809997685</v>
@@ -3782,16 +3779,16 @@
         <v>46244.62740439815</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>157</v>
       </c>
       <c r="I43" s="9">
         <v>46379</v>
@@ -3812,7 +3809,7 @@
         <v>132</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>132</v>
@@ -3835,7 +3832,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46237.56810440972</v>
@@ -3845,16 +3842,16 @@
         <v>46244.62751363426</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>156</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>157</v>
       </c>
       <c r="I44" s="5">
         <v>46379</v>
@@ -3872,13 +3869,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -3888,7 +3885,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B45" s="9">
         <v>46244.59380686343</v>
@@ -3904,10 +3901,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>157</v>
       </c>
       <c r="I45" s="9">
         <v>46379</v>
@@ -3925,13 +3922,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>65</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -3941,7 +3938,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B46" s="5">
         <v>46237.568445833334</v>
@@ -3951,7 +3948,7 @@
         <v>46244.60831364583</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -3975,7 +3972,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -3988,7 +3985,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B47" s="9">
         <v>46237.568449722225</v>
@@ -3998,16 +3995,16 @@
         <v>46244.62761877315</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="I47" s="9">
         <v>46247</v>
@@ -4025,13 +4022,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="Q47" s="9">
         <v>46338</v>
@@ -4051,7 +4048,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46244.60138324074</v>
@@ -4061,16 +4058,16 @@
         <v>46244.627581712964</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I48" s="5">
         <v>46337</v>
@@ -4088,13 +4085,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4104,7 +4101,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B49" s="9">
         <v>46244.60147203704</v>
@@ -4114,16 +4111,16 @@
         <v>46248.174775520834</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="I49" s="9">
         <v>46247</v>
@@ -4141,13 +4138,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4157,7 +4154,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B50" s="5">
         <v>46237.568459965274</v>
@@ -4167,16 +4164,16 @@
         <v>46267.18103443287</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I50" s="5">
         <v>46247</v>
@@ -4194,13 +4191,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4220,7 +4217,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B51" s="9">
         <v>46244.601417708334</v>
@@ -4230,16 +4227,16 @@
         <v>46266.17098471065</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="I51" s="9">
         <v>46265</v>
@@ -4257,13 +4254,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4273,7 +4270,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B52" s="5">
         <v>46244.60150188657</v>
@@ -4283,16 +4280,16 @@
         <v>46248.17477728009</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I52" s="5">
         <v>46247</v>
@@ -4310,13 +4307,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>61</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4326,7 +4323,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B53" s="9">
         <v>46237.568466979166</v>
@@ -4336,16 +4333,16 @@
         <v>46244.62774751158</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="I53" s="9">
         <v>46247</v>
@@ -4363,13 +4360,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O53" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="P53" s="10" t="s">
         <v>181</v>
-      </c>
-      <c r="P53" s="10" t="s">
-        <v>182</v>
       </c>
       <c r="Q53" s="9">
         <v>46371</v>
@@ -4389,7 +4386,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B54" s="5">
         <v>46244.60144362268</v>
@@ -4399,16 +4396,16 @@
         <v>46244.62780613426</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I54" s="5">
         <v>46370</v>
@@ -4426,13 +4423,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4442,7 +4439,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B55" s="9">
         <v>46244.60153101852</v>
@@ -4458,10 +4455,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="I55" s="9">
         <v>46247</v>
@@ -4479,13 +4476,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>64</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4495,7 +4492,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B56" s="5">
         <v>46244.60679788195</v>
@@ -4505,16 +4502,16 @@
         <v>46244.62786810185</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I56" s="5">
         <v>46352</v>
@@ -4532,7 +4529,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>125</v>
@@ -4558,7 +4555,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B57" s="9">
         <v>46237.568475821754</v>
@@ -4568,7 +4565,7 @@
         <v>46244.61656334491</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4592,7 +4589,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4605,7 +4602,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B58" s="5">
         <v>46237.56847953703</v>
@@ -4615,7 +4612,7 @@
         <v>46244.62806383102</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4642,13 +4639,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q58" s="5">
         <v>46359</v>
@@ -4668,7 +4665,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B59" s="9">
         <v>46237.56848447917</v>
@@ -4678,7 +4675,7 @@
         <v>46268.16902230324</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4705,13 +4702,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4721,7 +4718,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B60" s="5">
         <v>46237.56848827546</v>
@@ -4731,7 +4728,7 @@
         <v>46244.62802399306</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4758,13 +4755,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4774,7 +4771,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B61" s="9">
         <v>46237.56852555556</v>
@@ -4784,7 +4781,7 @@
         <v>46244.62816917824</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -4811,13 +4808,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q61" s="9">
         <v>46342</v>
@@ -4837,7 +4834,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B62" s="5">
         <v>46237.56853045139</v>
@@ -4847,7 +4844,7 @@
         <v>46252.17020165509</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -4874,13 +4871,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -4890,7 +4887,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B63" s="9">
         <v>46237.56853582176</v>
@@ -4900,7 +4897,7 @@
         <v>46244.62814572916</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -4927,13 +4924,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>200</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>201</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -4943,7 +4940,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B64" s="5">
         <v>46237.56863671297</v>
@@ -4953,7 +4950,7 @@
         <v>46244.62831047454</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -4980,13 +4977,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q64" s="5">
         <v>46373</v>
@@ -5006,7 +5003,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B65" s="9">
         <v>46237.5686419213</v>
@@ -5016,7 +5013,7 @@
         <v>46260.57276982639</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5043,13 +5040,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5061,7 +5058,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B66" s="5">
         <v>46237.56864618056</v>
@@ -5071,7 +5068,7 @@
         <v>46244.62826003472</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5098,13 +5095,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5114,7 +5111,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B67" s="9">
         <v>46237.568688796295</v>
@@ -5124,7 +5121,7 @@
         <v>46244.628418622684</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5151,13 +5148,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q67" s="9">
         <v>46374</v>
@@ -5177,7 +5174,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B68" s="5">
         <v>46237.568694120375</v>
@@ -5187,7 +5184,7 @@
         <v>46244.628406550924</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5214,13 +5211,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5230,7 +5227,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B69" s="9">
         <v>46237.5686980787</v>
@@ -5240,7 +5237,7 @@
         <v>46244.62839778935</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5267,13 +5264,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5283,7 +5280,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B70" s="5">
         <v>46237.5687887963</v>
@@ -5293,7 +5290,7 @@
         <v>46244.62847181713</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5320,13 +5317,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q70" s="5">
         <v>46377</v>
@@ -5346,7 +5343,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B71" s="9">
         <v>46237.56879706019</v>
@@ -5356,16 +5353,16 @@
         <v>46244.62853349537</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="I71" s="9">
         <v>46377</v>
@@ -5383,13 +5380,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5399,7 +5396,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B72" s="5">
         <v>46237.56880100694</v>
@@ -5409,16 +5406,16 @@
         <v>46244.62852962963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="I72" s="5">
         <v>46377</v>
@@ -5436,13 +5433,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5452,7 +5449,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B73" s="9">
         <v>46237.56883909722</v>
@@ -5462,7 +5459,7 @@
         <v>46244.6286615162</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5489,10 +5486,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5515,7 +5512,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B74" s="5">
         <v>46237.56884354167</v>
@@ -5525,7 +5522,7 @@
         <v>46244.62863414352</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5552,13 +5549,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5568,7 +5565,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B75" s="9">
         <v>46237.56884784722</v>
@@ -5605,13 +5602,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5621,7 +5618,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B76" s="5">
         <v>46237.56889393518</v>
@@ -5631,7 +5628,7 @@
         <v>46244.62875729166</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5658,10 +5655,10 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5684,7 +5681,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B77" s="9">
         <v>46237.56889887732</v>
@@ -5694,7 +5691,7 @@
         <v>46244.62873818287</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5721,13 +5718,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5737,7 +5734,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B78" s="5">
         <v>46237.568903437495</v>
@@ -5747,7 +5744,7 @@
         <v>46244.62873405093</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5774,13 +5771,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5790,7 +5787,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B79" s="9">
         <v>46237.56899291667</v>
@@ -5800,7 +5797,7 @@
         <v>46244.624352893516</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -5824,7 +5821,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -5837,7 +5834,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B80" s="5">
         <v>46237.568996898146</v>
@@ -5847,16 +5844,16 @@
         <v>46244.6288791088</v>
       </c>
       <c r="E80" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="6" t="s">
+      <c r="H80" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="I80" s="5">
         <v>46385</v>
@@ -5874,13 +5871,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q80" s="5">
         <v>46385</v>
@@ -5900,7 +5897,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B81" s="9">
         <v>46237.5690024537</v>
@@ -5910,16 +5907,16 @@
         <v>46244.629229375</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>237</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>238</v>
       </c>
       <c r="I81" s="9">
         <v>46385</v>
@@ -5937,13 +5934,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -5953,7 +5950,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B82" s="5">
         <v>46237.56900662037</v>
@@ -5963,16 +5960,16 @@
         <v>46244.62922577546</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="I82" s="5">
         <v>46385</v>
@@ -5990,13 +5987,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6006,7 +6003,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B83" s="9">
         <v>46237.56904663194</v>
@@ -6016,7 +6013,7 @@
         <v>46244.62915252315</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6043,10 +6040,10 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6069,7 +6066,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B84" s="5">
         <v>46237.56905172454</v>
@@ -6079,7 +6076,7 @@
         <v>46244.62902597222</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6106,13 +6103,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6122,7 +6119,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B85" s="9">
         <v>46237.56905527778</v>
@@ -6132,7 +6129,7 @@
         <v>46244.629022002315</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6159,13 +6156,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6175,7 +6172,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B86" s="5">
         <v>46237.569091666664</v>
@@ -6185,16 +6182,16 @@
         <v>46244.629364050925</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="I86" s="5">
         <v>46391</v>
@@ -6212,13 +6209,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q86" s="5">
         <v>46391</v>
@@ -6238,7 +6235,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B87" s="9">
         <v>46237.56913631945</v>
@@ -6248,16 +6245,16 @@
         <v>46244.62929709491</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="I87" s="9">
         <v>46391</v>
@@ -6275,13 +6272,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6291,7 +6288,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B88" s="5">
         <v>46237.5691418287</v>
@@ -6301,16 +6298,16 @@
         <v>46244.62929322917</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="I88" s="5">
         <v>46391</v>
@@ -6328,13 +6325,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6344,7 +6341,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B89" s="9">
         <v>46237.569190208334</v>
@@ -6354,16 +6351,16 @@
         <v>46244.629517615744</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="I89" s="9">
         <v>46392</v>
@@ -6381,13 +6378,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q89" s="9">
         <v>46392</v>
@@ -6407,7 +6404,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B90" s="5">
         <v>46237.56919672454</v>
@@ -6417,16 +6414,16 @@
         <v>46244.62945129629</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="I90" s="5">
         <v>46392</v>
@@ -6444,13 +6441,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6460,7 +6457,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B91" s="9">
         <v>46237.5692003588</v>
@@ -6470,16 +6467,16 @@
         <v>46244.62944737269</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="I91" s="9">
         <v>46392</v>
@@ -6497,13 +6494,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6513,7 +6510,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B92" s="5">
         <v>46237.569236180556</v>
@@ -6523,7 +6520,7 @@
         <v>46244.62474721065</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -6547,7 +6544,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -6560,7 +6557,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B93" s="9">
         <v>46237.56923991899</v>
@@ -6570,16 +6567,16 @@
         <v>46244.629587233794</v>
       </c>
       <c r="E93" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="F93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" s="10" t="s">
+      <c r="H93" s="10" t="s">
         <v>268</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>269</v>
       </c>
       <c r="I93" s="9">
         <v>46393</v>
@@ -6597,13 +6594,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q93" s="9">
         <v>46401</v>
@@ -6623,7 +6620,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B94" s="5">
         <v>46237.569245810184</v>
@@ -6633,16 +6630,16 @@
         <v>46244.62958366898</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I94" s="5">
         <v>46393</v>
@@ -6660,13 +6657,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q94" s="5">
         <v>46401</v>
